--- a/outputs/209-30.xlsx
+++ b/outputs/209-30.xlsx
@@ -30,10 +30,10 @@
     <t xml:space="preserve">URN</t>
   </si>
   <si>
-    <t xml:space="preserve">Location</t>
+    <t xml:space="preserve">The bug is in the line: c.Value = ("C2") = Left(ws.Range("C2"), Len(ws.Range("C2")) - 3). Here ("C2") is the literal text string "C2", not a reference to cell C2, so the expression ("C2") = Left(...) is a comparison that returns a Boolean (TRUE/FALSE). Since the string "C2" never equals the trimmed postcode, every cell is set to FALSE. The code also hard-codes ws.Range("C2") instead of using the loop variable c, so it would only act on row 2. The correct line is: c.Value = Left(c.Value, Len(c.Value) - 3)</t>
   </si>
   <si>
-    <t xml:space="preserve">DY8 </t>
+    <t xml:space="preserve">DY8 3NQ</t>
   </si>
 </sst>
 </file>
@@ -171,43 +171,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -215,15 +215,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/209-30.xlsx
+++ b/outputs/209-30.xlsx
@@ -30,10 +30,10 @@
     <t xml:space="preserve">URN</t>
   </si>
   <si>
-    <t xml:space="preserve">The bug is in the line: c.Value = ("C2") = Left(ws.Range("C2"), Len(ws.Range("C2")) - 3). Here ("C2") is the literal text string "C2", not a reference to cell C2, so the expression ("C2") = Left(...) is a comparison that returns a Boolean (TRUE/FALSE). Since the string "C2" never equals the trimmed postcode, every cell is set to FALSE. The code also hard-codes ws.Range("C2") instead of using the loop variable c, so it would only act on row 2. The correct line is: c.Value = Left(c.Value, Len(c.Value) - 3)</t>
+    <t xml:space="preserve">Location</t>
   </si>
   <si>
-    <t xml:space="preserve">DY8 3NQ</t>
+    <t xml:space="preserve">DY8 </t>
   </si>
 </sst>
 </file>
